--- a/data/trans_orig/IMC_inf_R2-Estudios-trans_orig.xlsx
+++ b/data/trans_orig/IMC_inf_R2-Estudios-trans_orig.xlsx
@@ -733,12 +733,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>18528</t>
+          <t>18674</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>31915</t>
+          <t>31084</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -748,12 +748,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>23,35%</t>
+          <t>23,54%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>40,23%</t>
+          <t>39,18%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -768,12 +768,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>28285</t>
+          <t>28220</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>41376</t>
+          <t>41364</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -783,12 +783,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>41,17%</t>
+          <t>41,07%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>60,22%</t>
+          <t>60,2%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -803,12 +803,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>49262</t>
+          <t>49565</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>68979</t>
+          <t>69387</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -818,12 +818,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>33,27%</t>
+          <t>33,48%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>46,59%</t>
+          <t>46,87%</t>
         </is>
       </c>
     </row>
@@ -846,12 +846,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>47420</t>
+          <t>48251</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>60807</t>
+          <t>60661</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -861,12 +861,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>59,77%</t>
+          <t>60,82%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>76,65%</t>
+          <t>76,46%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -881,12 +881,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>27333</t>
+          <t>27345</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>40424</t>
+          <t>40489</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -896,12 +896,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>39,78%</t>
+          <t>39,8%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>58,83%</t>
+          <t>58,93%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -916,12 +916,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>79065</t>
+          <t>78657</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>98782</t>
+          <t>98479</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -931,12 +931,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>53,41%</t>
+          <t>53,13%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>66,73%</t>
+          <t>66,52%</t>
         </is>
       </c>
     </row>
@@ -1076,12 +1076,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>111446</t>
+          <t>112282</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>141014</t>
+          <t>140288</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1091,12 +1091,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>31,65%</t>
+          <t>31,89%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>40,05%</t>
+          <t>39,84%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1111,12 +1111,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>183397</t>
+          <t>181156</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>214765</t>
+          <t>213176</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1126,12 +1126,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>44,73%</t>
+          <t>44,18%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>52,38%</t>
+          <t>51,99%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1146,12 +1146,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>302500</t>
+          <t>302363</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>345133</t>
+          <t>346194</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1161,12 +1161,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>39,69%</t>
+          <t>39,67%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>45,29%</t>
+          <t>45,42%</t>
         </is>
       </c>
     </row>
@@ -1189,12 +1189,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>211084</t>
+          <t>211810</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>240652</t>
+          <t>239816</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1204,12 +1204,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>59,95%</t>
+          <t>60,16%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>68,35%</t>
+          <t>68,11%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1224,12 +1224,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>195269</t>
+          <t>196858</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>226637</t>
+          <t>228878</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1239,12 +1239,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>47,62%</t>
+          <t>48,01%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>55,27%</t>
+          <t>55,82%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1259,12 +1259,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>416999</t>
+          <t>415938</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>459632</t>
+          <t>459769</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1274,12 +1274,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>54,71%</t>
+          <t>54,58%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>60,31%</t>
+          <t>60,33%</t>
         </is>
       </c>
     </row>
@@ -1419,12 +1419,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>44335</t>
+          <t>43833</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>63354</t>
+          <t>63367</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1434,12 +1434,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>30,23%</t>
+          <t>29,89%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>43,2%</t>
+          <t>43,21%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1454,12 +1454,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>32983</t>
+          <t>34388</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>49923</t>
+          <t>51314</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1469,12 +1469,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>26,03%</t>
+          <t>27,14%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>39,4%</t>
+          <t>40,5%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1489,12 +1489,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>83618</t>
+          <t>82675</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>109436</t>
+          <t>108050</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1504,12 +1504,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>30,59%</t>
+          <t>30,25%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>40,04%</t>
+          <t>39,53%</t>
         </is>
       </c>
     </row>
@@ -1532,12 +1532,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>83285</t>
+          <t>83272</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>102304</t>
+          <t>102806</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1547,12 +1547,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>56,8%</t>
+          <t>56,79%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>69,77%</t>
+          <t>70,11%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1567,12 +1567,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>76786</t>
+          <t>75395</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>93726</t>
+          <t>92321</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1582,12 +1582,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>60,6%</t>
+          <t>59,5%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>73,97%</t>
+          <t>72,86%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1602,12 +1602,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>163912</t>
+          <t>165298</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>189730</t>
+          <t>190673</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1617,12 +1617,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>59,96%</t>
+          <t>60,47%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>69,41%</t>
+          <t>69,75%</t>
         </is>
       </c>
     </row>
@@ -1762,12 +1762,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>187155</t>
+          <t>186354</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>221822</t>
+          <t>221172</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1777,12 +1777,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>32,38%</t>
+          <t>32,24%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>38,37%</t>
+          <t>38,26%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1797,12 +1797,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>255946</t>
+          <t>253811</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>295496</t>
+          <t>293625</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1812,12 +1812,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>42,27%</t>
+          <t>41,92%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>48,81%</t>
+          <t>48,5%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1832,12 +1832,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>452143</t>
+          <t>450305</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>506013</t>
+          <t>505438</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1847,12 +1847,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>38,2%</t>
+          <t>38,05%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>42,75%</t>
+          <t>42,71%</t>
         </is>
       </c>
     </row>
@@ -1875,12 +1875,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>356250</t>
+          <t>356900</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>390917</t>
+          <t>391718</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1890,12 +1890,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>61,63%</t>
+          <t>61,74%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>67,62%</t>
+          <t>67,76%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1910,12 +1910,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>309957</t>
+          <t>311828</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>349507</t>
+          <t>351642</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1925,12 +1925,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>51,19%</t>
+          <t>51,5%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>57,73%</t>
+          <t>58,08%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1945,12 +1945,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>677512</t>
+          <t>678087</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>731382</t>
+          <t>733220</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1960,12 +1960,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>57,25%</t>
+          <t>57,29%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>61,8%</t>
+          <t>61,95%</t>
         </is>
       </c>
     </row>
@@ -2336,12 +2336,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>23597</t>
+          <t>23118</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>36734</t>
+          <t>36258</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -2351,12 +2351,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>34,96%</t>
+          <t>34,25%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>54,42%</t>
+          <t>53,71%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -2371,12 +2371,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>22970</t>
+          <t>23664</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>36576</t>
+          <t>36399</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -2386,12 +2386,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>36,8%</t>
+          <t>37,91%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>58,59%</t>
+          <t>58,31%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -2406,12 +2406,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>49789</t>
+          <t>49718</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>67948</t>
+          <t>68456</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -2421,12 +2421,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>38,32%</t>
+          <t>38,26%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>52,29%</t>
+          <t>52,69%</t>
         </is>
       </c>
     </row>
@@ -2449,12 +2449,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>30772</t>
+          <t>31248</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>43909</t>
+          <t>44388</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -2464,12 +2464,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>45,58%</t>
+          <t>46,29%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>65,04%</t>
+          <t>65,75%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -2484,12 +2484,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>25851</t>
+          <t>26028</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>39457</t>
+          <t>38763</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -2499,12 +2499,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>41,41%</t>
+          <t>41,69%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>63,2%</t>
+          <t>62,09%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -2519,12 +2519,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>61985</t>
+          <t>61477</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>80144</t>
+          <t>80215</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -2534,12 +2534,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>47,71%</t>
+          <t>47,31%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>61,68%</t>
+          <t>61,74%</t>
         </is>
       </c>
     </row>
@@ -2679,12 +2679,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>128622</t>
+          <t>129439</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>158047</t>
+          <t>159603</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -2694,12 +2694,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>38,12%</t>
+          <t>38,36%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>46,84%</t>
+          <t>47,3%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -2714,12 +2714,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>170630</t>
+          <t>171135</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>202037</t>
+          <t>203064</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -2729,12 +2729,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>47,04%</t>
+          <t>47,18%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>55,7%</t>
+          <t>55,98%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -2749,12 +2749,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>309659</t>
+          <t>310538</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>352226</t>
+          <t>354625</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -2764,12 +2764,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>44,22%</t>
+          <t>44,35%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>50,3%</t>
+          <t>50,65%</t>
         </is>
       </c>
     </row>
@@ -2792,12 +2792,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>179401</t>
+          <t>177845</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>208826</t>
+          <t>208009</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -2807,12 +2807,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>53,16%</t>
+          <t>52,7%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>61,88%</t>
+          <t>61,64%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -2827,12 +2827,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>160707</t>
+          <t>159680</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>192114</t>
+          <t>191609</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -2842,12 +2842,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>44,3%</t>
+          <t>44,02%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>52,96%</t>
+          <t>52,82%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -2862,12 +2862,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>347966</t>
+          <t>345567</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>390533</t>
+          <t>389654</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -2877,12 +2877,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>49,7%</t>
+          <t>49,35%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>55,78%</t>
+          <t>55,65%</t>
         </is>
       </c>
     </row>
@@ -3022,12 +3022,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>39983</t>
+          <t>39602</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>57999</t>
+          <t>57473</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -3037,12 +3037,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>32,75%</t>
+          <t>32,44%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>47,51%</t>
+          <t>47,08%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -3057,12 +3057,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>54212</t>
+          <t>54742</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>73865</t>
+          <t>73284</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -3072,12 +3072,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>41,45%</t>
+          <t>41,85%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>56,47%</t>
+          <t>56,03%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -3092,12 +3092,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>99003</t>
+          <t>100957</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>125334</t>
+          <t>125271</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -3107,12 +3107,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>39,15%</t>
+          <t>39,92%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>49,56%</t>
+          <t>49,54%</t>
         </is>
       </c>
     </row>
@@ -3135,12 +3135,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>64077</t>
+          <t>64603</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>82093</t>
+          <t>82474</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -3150,12 +3150,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>52,49%</t>
+          <t>52,92%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>67,25%</t>
+          <t>67,56%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -3170,12 +3170,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>56934</t>
+          <t>57515</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>76587</t>
+          <t>76057</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -3185,12 +3185,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>43,53%</t>
+          <t>43,97%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>58,55%</t>
+          <t>58,15%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -3205,12 +3205,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>127541</t>
+          <t>127604</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>153872</t>
+          <t>151918</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -3220,12 +3220,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>50,44%</t>
+          <t>50,46%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>60,85%</t>
+          <t>60,08%</t>
         </is>
       </c>
     </row>
@@ -3365,12 +3365,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>201556</t>
+          <t>204318</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>239622</t>
+          <t>242337</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -3380,12 +3380,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>38,24%</t>
+          <t>38,77%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>45,47%</t>
+          <t>45,98%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -3400,12 +3400,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>261798</t>
+          <t>260692</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>301889</t>
+          <t>300656</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -3415,12 +3415,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>47,09%</t>
+          <t>46,89%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>54,3%</t>
+          <t>54,08%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -3435,12 +3435,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>475509</t>
+          <t>476298</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>528149</t>
+          <t>532717</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -3450,12 +3450,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>43,91%</t>
+          <t>43,98%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>48,77%</t>
+          <t>49,19%</t>
         </is>
       </c>
     </row>
@@ -3478,12 +3478,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>287408</t>
+          <t>284693</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>325474</t>
+          <t>322712</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -3493,12 +3493,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>54,53%</t>
+          <t>54,02%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>61,76%</t>
+          <t>61,23%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -3513,12 +3513,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>254081</t>
+          <t>255314</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>294172</t>
+          <t>295278</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -3528,12 +3528,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>45,7%</t>
+          <t>45,92%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>52,91%</t>
+          <t>53,11%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -3548,12 +3548,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>554851</t>
+          <t>550283</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>607491</t>
+          <t>606702</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -3563,12 +3563,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>51,23%</t>
+          <t>50,81%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>56,09%</t>
+          <t>56,02%</t>
         </is>
       </c>
     </row>
@@ -3939,12 +3939,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>21577</t>
+          <t>22090</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>32835</t>
+          <t>32619</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -3954,12 +3954,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>45,99%</t>
+          <t>47,08%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>69,99%</t>
+          <t>69,53%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -3974,12 +3974,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>22174</t>
+          <t>22761</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>34688</t>
+          <t>35040</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -3989,12 +3989,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>41,09%</t>
+          <t>42,17%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>64,27%</t>
+          <t>64,93%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -4009,12 +4009,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>47818</t>
+          <t>47727</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>62881</t>
+          <t>64117</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -4024,12 +4024,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>47,4%</t>
+          <t>47,31%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>62,33%</t>
+          <t>63,55%</t>
         </is>
       </c>
     </row>
@@ -4052,12 +4052,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>14081</t>
+          <t>14297</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>25339</t>
+          <t>24826</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -4067,12 +4067,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>30,01%</t>
+          <t>30,47%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>54,01%</t>
+          <t>52,92%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -4087,12 +4087,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>19281</t>
+          <t>18929</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>31795</t>
+          <t>31208</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -4102,12 +4102,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>35,73%</t>
+          <t>35,07%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>58,91%</t>
+          <t>57,83%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -4122,12 +4122,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>38004</t>
+          <t>36768</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>53067</t>
+          <t>53158</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -4137,12 +4137,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>37,67%</t>
+          <t>36,45%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>52,6%</t>
+          <t>52,69%</t>
         </is>
       </c>
     </row>
@@ -4282,12 +4282,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>110349</t>
+          <t>112405</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>141522</t>
+          <t>142085</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -4297,12 +4297,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>29,75%</t>
+          <t>30,31%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>38,16%</t>
+          <t>38,31%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -4317,12 +4317,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>155894</t>
+          <t>157143</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>189623</t>
+          <t>189664</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -4332,12 +4332,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>39,56%</t>
+          <t>39,88%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>48,12%</t>
+          <t>48,14%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -4352,12 +4352,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>277195</t>
+          <t>279021</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>322386</t>
+          <t>321491</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -4367,12 +4367,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>36,24%</t>
+          <t>36,48%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>42,15%</t>
+          <t>42,03%</t>
         </is>
       </c>
     </row>
@@ -4395,12 +4395,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>229345</t>
+          <t>228782</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>260518</t>
+          <t>258462</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -4410,12 +4410,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>61,84%</t>
+          <t>61,69%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>70,25%</t>
+          <t>69,69%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -4430,12 +4430,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>204399</t>
+          <t>204358</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>238128</t>
+          <t>236879</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -4445,12 +4445,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>51,88%</t>
+          <t>51,86%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>60,44%</t>
+          <t>60,12%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -4465,12 +4465,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>442503</t>
+          <t>443398</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>487694</t>
+          <t>485868</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -4480,12 +4480,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>57,85%</t>
+          <t>57,97%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>63,76%</t>
+          <t>63,52%</t>
         </is>
       </c>
     </row>
@@ -4625,12 +4625,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>28055</t>
+          <t>28837</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>44522</t>
+          <t>45615</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -4640,12 +4640,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>22,16%</t>
+          <t>22,77%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>35,16%</t>
+          <t>36,03%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -4660,12 +4660,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>50402</t>
+          <t>49861</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>69624</t>
+          <t>69557</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -4675,12 +4675,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>37,08%</t>
+          <t>36,68%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>51,22%</t>
+          <t>51,17%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -4695,12 +4695,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>83275</t>
+          <t>84065</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>109494</t>
+          <t>109123</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -4710,12 +4710,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>31,72%</t>
+          <t>32,02%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>41,7%</t>
+          <t>41,56%</t>
         </is>
       </c>
     </row>
@@ -4738,12 +4738,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>82097</t>
+          <t>81004</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>98564</t>
+          <t>97782</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -4753,12 +4753,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>64,84%</t>
+          <t>63,97%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>77,84%</t>
+          <t>77,23%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -4773,12 +4773,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>66318</t>
+          <t>66385</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>85540</t>
+          <t>86081</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -4788,12 +4788,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>48,78%</t>
+          <t>48,83%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>62,92%</t>
+          <t>63,32%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -4808,12 +4808,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>153067</t>
+          <t>153438</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>179286</t>
+          <t>178496</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -4823,12 +4823,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>58,3%</t>
+          <t>58,44%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>68,28%</t>
+          <t>67,98%</t>
         </is>
       </c>
     </row>
@@ -4968,12 +4968,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>170642</t>
+          <t>170586</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>208172</t>
+          <t>208083</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -4983,12 +4983,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>31,34%</t>
+          <t>31,33%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>38,24%</t>
+          <t>38,22%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -5003,12 +5003,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>241033</t>
+          <t>241538</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>280406</t>
+          <t>281183</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -5018,12 +5018,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>41,28%</t>
+          <t>41,36%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>48,02%</t>
+          <t>48,15%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -5038,12 +5038,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>425364</t>
+          <t>422726</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>481685</t>
+          <t>477154</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -5053,12 +5053,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>37,7%</t>
+          <t>37,46%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>42,69%</t>
+          <t>42,29%</t>
         </is>
       </c>
     </row>
@@ -5081,12 +5081,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>336230</t>
+          <t>336319</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>373760</t>
+          <t>373816</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -5096,12 +5096,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>61,76%</t>
+          <t>61,78%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>68,66%</t>
+          <t>68,67%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -5116,12 +5116,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>303528</t>
+          <t>302751</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>342901</t>
+          <t>342396</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -5131,12 +5131,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>51,98%</t>
+          <t>51,85%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>58,72%</t>
+          <t>58,64%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -5151,12 +5151,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>646651</t>
+          <t>651182</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>702972</t>
+          <t>705610</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -5166,12 +5166,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>57,31%</t>
+          <t>57,71%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>62,3%</t>
+          <t>62,54%</t>
         </is>
       </c>
     </row>
@@ -5542,12 +5542,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>9838</t>
+          <t>10227</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>26210</t>
+          <t>25799</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -5557,12 +5557,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>20,87%</t>
+          <t>21,7%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>55,61%</t>
+          <t>54,74%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -5577,12 +5577,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>12242</t>
+          <t>12695</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>24630</t>
+          <t>24701</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -5592,12 +5592,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>23,51%</t>
+          <t>24,38%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>47,3%</t>
+          <t>47,43%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -5612,12 +5612,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>26836</t>
+          <t>26490</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>46339</t>
+          <t>47615</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -5627,12 +5627,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>27,05%</t>
+          <t>26,7%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>46,71%</t>
+          <t>48,0%</t>
         </is>
       </c>
     </row>
@@ -5655,12 +5655,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>20921</t>
+          <t>21332</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>37293</t>
+          <t>36904</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -5670,12 +5670,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>44,39%</t>
+          <t>45,26%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>79,13%</t>
+          <t>78,3%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -5690,12 +5690,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>27447</t>
+          <t>27376</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>39835</t>
+          <t>39382</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -5705,12 +5705,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>52,7%</t>
+          <t>52,57%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>76,49%</t>
+          <t>75,62%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -5725,12 +5725,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>52869</t>
+          <t>51593</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>72372</t>
+          <t>72718</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -5740,12 +5740,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>53,29%</t>
+          <t>52,0%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>72,95%</t>
+          <t>73,3%</t>
         </is>
       </c>
     </row>
@@ -5885,12 +5885,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>88057</t>
+          <t>87441</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>129876</t>
+          <t>128619</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -5900,12 +5900,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>22,41%</t>
+          <t>22,25%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>33,05%</t>
+          <t>32,73%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -5920,12 +5920,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>166750</t>
+          <t>169339</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>212401</t>
+          <t>215052</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -5935,12 +5935,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>36,86%</t>
+          <t>37,43%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>46,95%</t>
+          <t>47,54%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -5955,12 +5955,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>267354</t>
+          <t>264947</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>334991</t>
+          <t>333492</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -5970,12 +5970,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>31,63%</t>
+          <t>31,34%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>39,63%</t>
+          <t>39,45%</t>
         </is>
       </c>
     </row>
@@ -5998,12 +5998,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>263057</t>
+          <t>264314</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>304876</t>
+          <t>305492</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -6013,12 +6013,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>66,95%</t>
+          <t>67,27%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>77,59%</t>
+          <t>77,75%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -6033,12 +6033,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>239973</t>
+          <t>237322</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>285624</t>
+          <t>283035</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -6048,12 +6048,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>53,05%</t>
+          <t>52,46%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>63,14%</t>
+          <t>62,57%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -6068,12 +6068,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>510316</t>
+          <t>511815</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>577953</t>
+          <t>580360</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -6083,12 +6083,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>60,37%</t>
+          <t>60,55%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>68,37%</t>
+          <t>68,66%</t>
         </is>
       </c>
     </row>
@@ -6228,12 +6228,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>23036</t>
+          <t>23216</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>39578</t>
+          <t>39252</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -6243,12 +6243,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>17,21%</t>
+          <t>17,34%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>29,56%</t>
+          <t>29,32%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -6263,12 +6263,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>35485</t>
+          <t>36110</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>55559</t>
+          <t>56087</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -6278,12 +6278,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>23,91%</t>
+          <t>24,33%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>37,44%</t>
+          <t>37,79%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -6298,12 +6298,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>64173</t>
+          <t>65240</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>89516</t>
+          <t>91376</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -6313,12 +6313,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>22,73%</t>
+          <t>23,11%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>31,71%</t>
+          <t>32,37%</t>
         </is>
       </c>
     </row>
@@ -6341,12 +6341,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>94311</t>
+          <t>94637</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>110853</t>
+          <t>110673</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -6356,12 +6356,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>70,44%</t>
+          <t>70,68%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>82,79%</t>
+          <t>82,66%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -6376,12 +6376,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>92841</t>
+          <t>92313</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>112915</t>
+          <t>112290</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -6391,12 +6391,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>62,56%</t>
+          <t>62,21%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>76,09%</t>
+          <t>75,67%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -6411,12 +6411,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>192774</t>
+          <t>190914</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>218117</t>
+          <t>217050</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -6426,12 +6426,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>68,29%</t>
+          <t>67,63%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>77,27%</t>
+          <t>76,89%</t>
         </is>
       </c>
     </row>
@@ -6571,12 +6571,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>136889</t>
+          <t>136551</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>184399</t>
+          <t>184022</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -6586,12 +6586,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>23,85%</t>
+          <t>23,79%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>32,13%</t>
+          <t>32,06%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -6606,12 +6606,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>229878</t>
+          <t>228801</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>282178</t>
+          <t>279715</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -6621,12 +6621,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>35,21%</t>
+          <t>35,05%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>43,22%</t>
+          <t>42,85%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -6641,12 +6641,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>378202</t>
+          <t>379010</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>453025</t>
+          <t>448946</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -6656,12 +6656,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>30,83%</t>
+          <t>30,89%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>36,93%</t>
+          <t>36,59%</t>
         </is>
       </c>
     </row>
@@ -6684,12 +6684,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>389554</t>
+          <t>389931</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>437064</t>
+          <t>437402</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -6699,12 +6699,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>67,87%</t>
+          <t>67,94%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>76,15%</t>
+          <t>76,21%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -6719,12 +6719,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>370674</t>
+          <t>373137</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>422974</t>
+          <t>424051</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -6734,12 +6734,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>56,78%</t>
+          <t>57,15%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>64,79%</t>
+          <t>64,95%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -6754,12 +6754,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>773780</t>
+          <t>777859</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>848603</t>
+          <t>847795</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -6769,12 +6769,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>63,07%</t>
+          <t>63,41%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>69,17%</t>
+          <t>69,11%</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/IMC_inf_R2-Estudios-trans_orig.xlsx
+++ b/data/trans_orig/IMC_inf_R2-Estudios-trans_orig.xlsx
@@ -544,7 +544,7 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -555,7 +555,7 @@
       <c r="I1" s="3" t="n"/>
       <c r="J1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="K1" s="3" t="n"/>
@@ -723,72 +723,72 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>51</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>34384</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>27978</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>40719</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>50,04%</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>40,72%</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>59,26%</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
           <t>39</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="K4" s="2" t="inlineStr">
         <is>
           <t>24602</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>18674</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>31084</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
+      <c r="L4" s="2" t="inlineStr">
+        <is>
+          <t>17969</t>
+        </is>
+      </c>
+      <c r="M4" s="2" t="inlineStr">
+        <is>
+          <t>31338</t>
+        </is>
+      </c>
+      <c r="N4" s="2" t="inlineStr">
         <is>
           <t>31,01%</t>
         </is>
       </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>23,54%</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>39,18%</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>51</t>
-        </is>
-      </c>
-      <c r="K4" s="2" t="inlineStr">
-        <is>
-          <t>34384</t>
-        </is>
-      </c>
-      <c r="L4" s="2" t="inlineStr">
-        <is>
-          <t>28220</t>
-        </is>
-      </c>
-      <c r="M4" s="2" t="inlineStr">
-        <is>
-          <t>41364</t>
-        </is>
-      </c>
-      <c r="N4" s="2" t="inlineStr">
-        <is>
-          <t>50,04%</t>
-        </is>
-      </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>41,07%</t>
+          <t>22,65%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>60,2%</t>
+          <t>39,5%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -803,12 +803,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>49565</t>
+          <t>49351</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>69387</t>
+          <t>69231</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -818,12 +818,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>33,48%</t>
+          <t>33,34%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>46,87%</t>
+          <t>46,76%</t>
         </is>
       </c>
     </row>
@@ -836,72 +836,72 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
+          <t>52</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>34325</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>27990</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>40731</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>49,96%</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>40,74%</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>59,28%</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
           <t>80</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
+      <c r="K5" s="2" t="inlineStr">
         <is>
           <t>54733</t>
         </is>
       </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>48251</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>60661</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
+      <c r="L5" s="2" t="inlineStr">
+        <is>
+          <t>47997</t>
+        </is>
+      </c>
+      <c r="M5" s="2" t="inlineStr">
+        <is>
+          <t>61366</t>
+        </is>
+      </c>
+      <c r="N5" s="2" t="inlineStr">
         <is>
           <t>68,99%</t>
         </is>
       </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>60,82%</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>76,46%</t>
-        </is>
-      </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>52</t>
-        </is>
-      </c>
-      <c r="K5" s="2" t="inlineStr">
-        <is>
-          <t>34325</t>
-        </is>
-      </c>
-      <c r="L5" s="2" t="inlineStr">
-        <is>
-          <t>27345</t>
-        </is>
-      </c>
-      <c r="M5" s="2" t="inlineStr">
-        <is>
-          <t>40489</t>
-        </is>
-      </c>
-      <c r="N5" s="2" t="inlineStr">
-        <is>
-          <t>49,96%</t>
-        </is>
-      </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>39,8%</t>
+          <t>60,5%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>58,93%</t>
+          <t>77,35%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -916,12 +916,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>78657</t>
+          <t>78813</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>98479</t>
+          <t>98693</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -931,12 +931,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>53,13%</t>
+          <t>53,24%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>66,52%</t>
+          <t>66,66%</t>
         </is>
       </c>
     </row>
@@ -949,57 +949,57 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>103</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>68709</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>68709</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>68709</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
           <t>119</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="K6" s="2" t="inlineStr">
         <is>
           <t>79335</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
+      <c r="L6" s="2" t="inlineStr">
         <is>
           <t>79335</t>
         </is>
       </c>
-      <c r="F6" s="2" t="inlineStr">
+      <c r="M6" s="2" t="inlineStr">
         <is>
           <t>79335</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>103</t>
-        </is>
-      </c>
-      <c r="K6" s="2" t="inlineStr">
-        <is>
-          <t>68709</t>
-        </is>
-      </c>
-      <c r="L6" s="2" t="inlineStr">
-        <is>
-          <t>68709</t>
-        </is>
-      </c>
-      <c r="M6" s="2" t="inlineStr">
-        <is>
-          <t>68709</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1066,72 +1066,72 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
+          <t>299</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>198190</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>182212</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>214678</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>48,33%</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>44,44%</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>52,36%</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
           <t>193</t>
         </is>
       </c>
-      <c r="D7" s="2" t="inlineStr">
+      <c r="K7" s="2" t="inlineStr">
         <is>
           <t>125755</t>
         </is>
       </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>112282</t>
-        </is>
-      </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>140288</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
+      <c r="L7" s="2" t="inlineStr">
+        <is>
+          <t>112000</t>
+        </is>
+      </c>
+      <c r="M7" s="2" t="inlineStr">
+        <is>
+          <t>141238</t>
+        </is>
+      </c>
+      <c r="N7" s="2" t="inlineStr">
         <is>
           <t>35,72%</t>
         </is>
       </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>31,89%</t>
-        </is>
-      </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>39,84%</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>299</t>
-        </is>
-      </c>
-      <c r="K7" s="2" t="inlineStr">
-        <is>
-          <t>198190</t>
-        </is>
-      </c>
-      <c r="L7" s="2" t="inlineStr">
-        <is>
-          <t>181156</t>
-        </is>
-      </c>
-      <c r="M7" s="2" t="inlineStr">
-        <is>
-          <t>213176</t>
-        </is>
-      </c>
-      <c r="N7" s="2" t="inlineStr">
-        <is>
-          <t>48,33%</t>
-        </is>
-      </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>44,18%</t>
+          <t>31,81%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>51,99%</t>
+          <t>40,11%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1146,12 +1146,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>302363</t>
+          <t>301966</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>346194</t>
+          <t>344158</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1161,12 +1161,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>39,67%</t>
+          <t>39,62%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>45,42%</t>
+          <t>45,16%</t>
         </is>
       </c>
     </row>
@@ -1179,72 +1179,72 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>320</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>211844</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>195356</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>227822</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>51,67%</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>47,64%</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>55,56%</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
           <t>338</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="K8" s="2" t="inlineStr">
         <is>
           <t>226343</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>211810</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>239816</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
+      <c r="L8" s="2" t="inlineStr">
+        <is>
+          <t>210860</t>
+        </is>
+      </c>
+      <c r="M8" s="2" t="inlineStr">
+        <is>
+          <t>240098</t>
+        </is>
+      </c>
+      <c r="N8" s="2" t="inlineStr">
         <is>
           <t>64,28%</t>
         </is>
       </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>60,16%</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>68,11%</t>
-        </is>
-      </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>320</t>
-        </is>
-      </c>
-      <c r="K8" s="2" t="inlineStr">
-        <is>
-          <t>211844</t>
-        </is>
-      </c>
-      <c r="L8" s="2" t="inlineStr">
-        <is>
-          <t>196858</t>
-        </is>
-      </c>
-      <c r="M8" s="2" t="inlineStr">
-        <is>
-          <t>228878</t>
-        </is>
-      </c>
-      <c r="N8" s="2" t="inlineStr">
-        <is>
-          <t>51,67%</t>
-        </is>
-      </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>48,01%</t>
+          <t>59,89%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>55,82%</t>
+          <t>68,19%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1259,12 +1259,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>415938</t>
+          <t>417974</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>459769</t>
+          <t>460166</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1274,12 +1274,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>54,58%</t>
+          <t>54,84%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>60,33%</t>
+          <t>60,38%</t>
         </is>
       </c>
     </row>
@@ -1292,57 +1292,57 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
+          <t>619</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>410034</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>410034</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>410034</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
           <t>531</t>
         </is>
       </c>
-      <c r="D9" s="2" t="inlineStr">
+      <c r="K9" s="2" t="inlineStr">
         <is>
           <t>352098</t>
         </is>
       </c>
-      <c r="E9" s="2" t="inlineStr">
+      <c r="L9" s="2" t="inlineStr">
         <is>
           <t>352098</t>
         </is>
       </c>
-      <c r="F9" s="2" t="inlineStr">
+      <c r="M9" s="2" t="inlineStr">
         <is>
           <t>352098</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>619</t>
-        </is>
-      </c>
-      <c r="K9" s="2" t="inlineStr">
-        <is>
-          <t>410034</t>
-        </is>
-      </c>
-      <c r="L9" s="2" t="inlineStr">
-        <is>
-          <t>410034</t>
-        </is>
-      </c>
-      <c r="M9" s="2" t="inlineStr">
-        <is>
-          <t>410034</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -1409,72 +1409,72 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>64</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>42416</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>34831</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>51518</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>33,48%</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>27,49%</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>40,66%</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
           <t>77</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="K10" s="2" t="inlineStr">
         <is>
           <t>53368</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>43833</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>63367</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
+      <c r="L10" s="2" t="inlineStr">
+        <is>
+          <t>44111</t>
+        </is>
+      </c>
+      <c r="M10" s="2" t="inlineStr">
+        <is>
+          <t>62689</t>
+        </is>
+      </c>
+      <c r="N10" s="2" t="inlineStr">
         <is>
           <t>36,39%</t>
         </is>
       </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>29,89%</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>43,21%</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>64</t>
-        </is>
-      </c>
-      <c r="K10" s="2" t="inlineStr">
-        <is>
-          <t>42416</t>
-        </is>
-      </c>
-      <c r="L10" s="2" t="inlineStr">
-        <is>
-          <t>34388</t>
-        </is>
-      </c>
-      <c r="M10" s="2" t="inlineStr">
-        <is>
-          <t>51314</t>
-        </is>
-      </c>
-      <c r="N10" s="2" t="inlineStr">
-        <is>
-          <t>33,48%</t>
-        </is>
-      </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>27,14%</t>
+          <t>30,08%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>40,5%</t>
+          <t>42,75%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1489,12 +1489,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>82675</t>
+          <t>82810</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>108050</t>
+          <t>109022</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1504,12 +1504,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>30,25%</t>
+          <t>30,29%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>39,53%</t>
+          <t>39,88%</t>
         </is>
       </c>
     </row>
@@ -1522,72 +1522,72 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
+          <t>124</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>84293</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>75191</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>91878</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>66,52%</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>59,34%</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>72,51%</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
           <t>136</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
+      <c r="K11" s="2" t="inlineStr">
         <is>
           <t>93271</t>
         </is>
       </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>83272</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>102806</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
+      <c r="L11" s="2" t="inlineStr">
+        <is>
+          <t>83950</t>
+        </is>
+      </c>
+      <c r="M11" s="2" t="inlineStr">
+        <is>
+          <t>102528</t>
+        </is>
+      </c>
+      <c r="N11" s="2" t="inlineStr">
         <is>
           <t>63,61%</t>
         </is>
       </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>56,79%</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>70,11%</t>
-        </is>
-      </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>124</t>
-        </is>
-      </c>
-      <c r="K11" s="2" t="inlineStr">
-        <is>
-          <t>84293</t>
-        </is>
-      </c>
-      <c r="L11" s="2" t="inlineStr">
-        <is>
-          <t>75395</t>
-        </is>
-      </c>
-      <c r="M11" s="2" t="inlineStr">
-        <is>
-          <t>92321</t>
-        </is>
-      </c>
-      <c r="N11" s="2" t="inlineStr">
-        <is>
-          <t>66,52%</t>
-        </is>
-      </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>59,5%</t>
+          <t>57,25%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>72,86%</t>
+          <t>69,92%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1602,12 +1602,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>165298</t>
+          <t>164326</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>190673</t>
+          <t>190538</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1617,12 +1617,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>60,47%</t>
+          <t>60,12%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>69,75%</t>
+          <t>69,71%</t>
         </is>
       </c>
     </row>
@@ -1635,57 +1635,57 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>188</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>126709</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>126709</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>126709</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
           <t>213</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
+      <c r="K12" s="2" t="inlineStr">
         <is>
           <t>146639</t>
         </is>
       </c>
-      <c r="E12" s="2" t="inlineStr">
+      <c r="L12" s="2" t="inlineStr">
         <is>
           <t>146639</t>
         </is>
       </c>
-      <c r="F12" s="2" t="inlineStr">
+      <c r="M12" s="2" t="inlineStr">
         <is>
           <t>146639</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J12" s="2" t="inlineStr">
-        <is>
-          <t>188</t>
-        </is>
-      </c>
-      <c r="K12" s="2" t="inlineStr">
-        <is>
-          <t>126709</t>
-        </is>
-      </c>
-      <c r="L12" s="2" t="inlineStr">
-        <is>
-          <t>126709</t>
-        </is>
-      </c>
-      <c r="M12" s="2" t="inlineStr">
-        <is>
-          <t>126709</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1752,72 +1752,72 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
+          <t>414</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>274990</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>255865</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>293526</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>45,42%</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>42,26%</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>48,48%</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
           <t>309</t>
         </is>
       </c>
-      <c r="D13" s="2" t="inlineStr">
+      <c r="K13" s="2" t="inlineStr">
         <is>
           <t>203724</t>
         </is>
       </c>
-      <c r="E13" s="2" t="inlineStr">
-        <is>
-          <t>186354</t>
-        </is>
-      </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>221172</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
+      <c r="L13" s="2" t="inlineStr">
+        <is>
+          <t>186635</t>
+        </is>
+      </c>
+      <c r="M13" s="2" t="inlineStr">
+        <is>
+          <t>223096</t>
+        </is>
+      </c>
+      <c r="N13" s="2" t="inlineStr">
         <is>
           <t>35,24%</t>
         </is>
       </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>32,24%</t>
-        </is>
-      </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>38,26%</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>414</t>
-        </is>
-      </c>
-      <c r="K13" s="2" t="inlineStr">
-        <is>
-          <t>274990</t>
-        </is>
-      </c>
-      <c r="L13" s="2" t="inlineStr">
-        <is>
-          <t>253811</t>
-        </is>
-      </c>
-      <c r="M13" s="2" t="inlineStr">
-        <is>
-          <t>293625</t>
-        </is>
-      </c>
-      <c r="N13" s="2" t="inlineStr">
-        <is>
-          <t>45,42%</t>
-        </is>
-      </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>41,92%</t>
+          <t>32,29%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>48,5%</t>
+          <t>38,59%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1832,12 +1832,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>450305</t>
+          <t>450692</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>505438</t>
+          <t>504253</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1847,12 +1847,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>38,05%</t>
+          <t>38,08%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>42,71%</t>
+          <t>42,61%</t>
         </is>
       </c>
     </row>
@@ -1865,72 +1865,72 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>496</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>330463</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>311927</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>349588</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>54,58%</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>51,52%</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>57,74%</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
           <t>554</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="K14" s="2" t="inlineStr">
         <is>
           <t>374348</t>
         </is>
       </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>356900</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>391718</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
+      <c r="L14" s="2" t="inlineStr">
+        <is>
+          <t>354976</t>
+        </is>
+      </c>
+      <c r="M14" s="2" t="inlineStr">
+        <is>
+          <t>391437</t>
+        </is>
+      </c>
+      <c r="N14" s="2" t="inlineStr">
         <is>
           <t>64,76%</t>
         </is>
       </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>61,74%</t>
-        </is>
-      </c>
-      <c r="I14" s="2" t="inlineStr">
-        <is>
-          <t>67,76%</t>
-        </is>
-      </c>
-      <c r="J14" s="2" t="inlineStr">
-        <is>
-          <t>496</t>
-        </is>
-      </c>
-      <c r="K14" s="2" t="inlineStr">
-        <is>
-          <t>330463</t>
-        </is>
-      </c>
-      <c r="L14" s="2" t="inlineStr">
-        <is>
-          <t>311828</t>
-        </is>
-      </c>
-      <c r="M14" s="2" t="inlineStr">
-        <is>
-          <t>351642</t>
-        </is>
-      </c>
-      <c r="N14" s="2" t="inlineStr">
-        <is>
-          <t>54,58%</t>
-        </is>
-      </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>51,5%</t>
+          <t>61,41%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>58,08%</t>
+          <t>67,71%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1945,12 +1945,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>678087</t>
+          <t>679272</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>733220</t>
+          <t>732833</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1960,12 +1960,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>57,29%</t>
+          <t>57,39%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>61,95%</t>
+          <t>61,92%</t>
         </is>
       </c>
     </row>
@@ -1978,57 +1978,57 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
+          <t>910</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>605453</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>605453</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>605453</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
           <t>863</t>
         </is>
       </c>
-      <c r="D15" s="2" t="inlineStr">
+      <c r="K15" s="2" t="inlineStr">
         <is>
           <t>578072</t>
         </is>
       </c>
-      <c r="E15" s="2" t="inlineStr">
+      <c r="L15" s="2" t="inlineStr">
         <is>
           <t>578072</t>
         </is>
       </c>
-      <c r="F15" s="2" t="inlineStr">
+      <c r="M15" s="2" t="inlineStr">
         <is>
           <t>578072</t>
-        </is>
-      </c>
-      <c r="G15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J15" s="2" t="inlineStr">
-        <is>
-          <t>910</t>
-        </is>
-      </c>
-      <c r="K15" s="2" t="inlineStr">
-        <is>
-          <t>605453</t>
-        </is>
-      </c>
-      <c r="L15" s="2" t="inlineStr">
-        <is>
-          <t>605453</t>
-        </is>
-      </c>
-      <c r="M15" s="2" t="inlineStr">
-        <is>
-          <t>605453</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -2147,7 +2147,7 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -2158,7 +2158,7 @@
       <c r="I1" s="3" t="n"/>
       <c r="J1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="K1" s="3" t="n"/>
@@ -2331,67 +2331,67 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
+          <t>29244</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>22605</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>35403</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>46,84%</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>36,21%</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>56,71%</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
+          <t>43</t>
+        </is>
+      </c>
+      <c r="K4" s="2" t="inlineStr">
+        <is>
           <t>29945</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>23118</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>36258</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
+      <c r="L4" s="2" t="inlineStr">
+        <is>
+          <t>23244</t>
+        </is>
+      </c>
+      <c r="M4" s="2" t="inlineStr">
+        <is>
+          <t>36832</t>
+        </is>
+      </c>
+      <c r="N4" s="2" t="inlineStr">
         <is>
           <t>44,36%</t>
         </is>
       </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>34,25%</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>53,71%</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>43</t>
-        </is>
-      </c>
-      <c r="K4" s="2" t="inlineStr">
-        <is>
-          <t>29244</t>
-        </is>
-      </c>
-      <c r="L4" s="2" t="inlineStr">
-        <is>
-          <t>23664</t>
-        </is>
-      </c>
-      <c r="M4" s="2" t="inlineStr">
-        <is>
-          <t>36399</t>
-        </is>
-      </c>
-      <c r="N4" s="2" t="inlineStr">
-        <is>
-          <t>46,84%</t>
-        </is>
-      </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>37,91%</t>
+          <t>34,43%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>58,31%</t>
+          <t>54,56%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -2406,12 +2406,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>49718</t>
+          <t>50455</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>68456</t>
+          <t>67999</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -2421,12 +2421,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>38,26%</t>
+          <t>38,83%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>52,69%</t>
+          <t>52,33%</t>
         </is>
       </c>
     </row>
@@ -2439,72 +2439,72 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
+          <t>46</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>33183</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>27024</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>39822</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>53,16%</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>43,29%</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>63,79%</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
           <t>54</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
+      <c r="K5" s="2" t="inlineStr">
         <is>
           <t>37561</t>
         </is>
       </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>31248</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>44388</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
+      <c r="L5" s="2" t="inlineStr">
+        <is>
+          <t>30674</t>
+        </is>
+      </c>
+      <c r="M5" s="2" t="inlineStr">
+        <is>
+          <t>44262</t>
+        </is>
+      </c>
+      <c r="N5" s="2" t="inlineStr">
         <is>
           <t>55,64%</t>
         </is>
       </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>46,29%</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>65,75%</t>
-        </is>
-      </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>46</t>
-        </is>
-      </c>
-      <c r="K5" s="2" t="inlineStr">
-        <is>
-          <t>33183</t>
-        </is>
-      </c>
-      <c r="L5" s="2" t="inlineStr">
-        <is>
-          <t>26028</t>
-        </is>
-      </c>
-      <c r="M5" s="2" t="inlineStr">
-        <is>
-          <t>38763</t>
-        </is>
-      </c>
-      <c r="N5" s="2" t="inlineStr">
-        <is>
-          <t>53,16%</t>
-        </is>
-      </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>41,69%</t>
+          <t>45,44%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>62,09%</t>
+          <t>65,57%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -2519,12 +2519,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>61477</t>
+          <t>61934</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>80215</t>
+          <t>79478</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -2534,12 +2534,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>47,31%</t>
+          <t>47,67%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>61,74%</t>
+          <t>61,17%</t>
         </is>
       </c>
     </row>
@@ -2552,57 +2552,57 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>89</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>62427</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>62427</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>62427</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
           <t>97</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="K6" s="2" t="inlineStr">
         <is>
           <t>67506</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
+      <c r="L6" s="2" t="inlineStr">
         <is>
           <t>67506</t>
         </is>
       </c>
-      <c r="F6" s="2" t="inlineStr">
+      <c r="M6" s="2" t="inlineStr">
         <is>
           <t>67506</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>89</t>
-        </is>
-      </c>
-      <c r="K6" s="2" t="inlineStr">
-        <is>
-          <t>62427</t>
-        </is>
-      </c>
-      <c r="L6" s="2" t="inlineStr">
-        <is>
-          <t>62427</t>
-        </is>
-      </c>
-      <c r="M6" s="2" t="inlineStr">
-        <is>
-          <t>62427</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -2669,72 +2669,72 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
+          <t>270</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>187390</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>170684</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>202764</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>51,66%</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>47,05%</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>55,9%</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
           <t>206</t>
         </is>
       </c>
-      <c r="D7" s="2" t="inlineStr">
+      <c r="K7" s="2" t="inlineStr">
         <is>
           <t>144001</t>
         </is>
       </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>129439</t>
-        </is>
-      </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>159603</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
+      <c r="L7" s="2" t="inlineStr">
+        <is>
+          <t>128551</t>
+        </is>
+      </c>
+      <c r="M7" s="2" t="inlineStr">
+        <is>
+          <t>158155</t>
+        </is>
+      </c>
+      <c r="N7" s="2" t="inlineStr">
         <is>
           <t>42,67%</t>
         </is>
       </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>38,36%</t>
-        </is>
-      </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>47,3%</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>270</t>
-        </is>
-      </c>
-      <c r="K7" s="2" t="inlineStr">
-        <is>
-          <t>187390</t>
-        </is>
-      </c>
-      <c r="L7" s="2" t="inlineStr">
-        <is>
-          <t>171135</t>
-        </is>
-      </c>
-      <c r="M7" s="2" t="inlineStr">
-        <is>
-          <t>203064</t>
-        </is>
-      </c>
-      <c r="N7" s="2" t="inlineStr">
-        <is>
-          <t>51,66%</t>
-        </is>
-      </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>47,18%</t>
+          <t>38,1%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>55,98%</t>
+          <t>46,87%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -2749,12 +2749,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>310538</t>
+          <t>310597</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>354625</t>
+          <t>352177</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -2764,12 +2764,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>44,35%</t>
+          <t>44,36%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>50,65%</t>
+          <t>50,3%</t>
         </is>
       </c>
     </row>
@@ -2782,72 +2782,72 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>253</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>175354</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>159980</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>192060</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>48,34%</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>44,1%</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>52,95%</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
           <t>282</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="K8" s="2" t="inlineStr">
         <is>
           <t>193447</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>177845</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>208009</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
+      <c r="L8" s="2" t="inlineStr">
+        <is>
+          <t>179293</t>
+        </is>
+      </c>
+      <c r="M8" s="2" t="inlineStr">
+        <is>
+          <t>208897</t>
+        </is>
+      </c>
+      <c r="N8" s="2" t="inlineStr">
         <is>
           <t>57,33%</t>
         </is>
       </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>52,7%</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>61,64%</t>
-        </is>
-      </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>253</t>
-        </is>
-      </c>
-      <c r="K8" s="2" t="inlineStr">
-        <is>
-          <t>175354</t>
-        </is>
-      </c>
-      <c r="L8" s="2" t="inlineStr">
-        <is>
-          <t>159680</t>
-        </is>
-      </c>
-      <c r="M8" s="2" t="inlineStr">
-        <is>
-          <t>191609</t>
-        </is>
-      </c>
-      <c r="N8" s="2" t="inlineStr">
-        <is>
-          <t>48,34%</t>
-        </is>
-      </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>44,02%</t>
+          <t>53,13%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>52,82%</t>
+          <t>61,9%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -2862,12 +2862,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>345567</t>
+          <t>348015</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>389654</t>
+          <t>389595</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -2877,12 +2877,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>49,35%</t>
+          <t>49,7%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>55,65%</t>
+          <t>55,64%</t>
         </is>
       </c>
     </row>
@@ -2895,57 +2895,57 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
+          <t>523</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>362744</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>362744</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>362744</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
           <t>488</t>
         </is>
       </c>
-      <c r="D9" s="2" t="inlineStr">
+      <c r="K9" s="2" t="inlineStr">
         <is>
           <t>337448</t>
         </is>
       </c>
-      <c r="E9" s="2" t="inlineStr">
+      <c r="L9" s="2" t="inlineStr">
         <is>
           <t>337448</t>
         </is>
       </c>
-      <c r="F9" s="2" t="inlineStr">
+      <c r="M9" s="2" t="inlineStr">
         <is>
           <t>337448</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>523</t>
-        </is>
-      </c>
-      <c r="K9" s="2" t="inlineStr">
-        <is>
-          <t>362744</t>
-        </is>
-      </c>
-      <c r="L9" s="2" t="inlineStr">
-        <is>
-          <t>362744</t>
-        </is>
-      </c>
-      <c r="M9" s="2" t="inlineStr">
-        <is>
-          <t>362744</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -3012,72 +3012,72 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>91</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>64357</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>55373</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>73961</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>49,2%</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>42,33%</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>56,55%</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
           <t>68</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="K10" s="2" t="inlineStr">
         <is>
           <t>48220</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>39602</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>57473</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
+      <c r="L10" s="2" t="inlineStr">
+        <is>
+          <t>38483</t>
+        </is>
+      </c>
+      <c r="M10" s="2" t="inlineStr">
+        <is>
+          <t>57493</t>
+        </is>
+      </c>
+      <c r="N10" s="2" t="inlineStr">
         <is>
           <t>39,5%</t>
         </is>
       </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>32,44%</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>47,08%</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>91</t>
-        </is>
-      </c>
-      <c r="K10" s="2" t="inlineStr">
-        <is>
-          <t>64357</t>
-        </is>
-      </c>
-      <c r="L10" s="2" t="inlineStr">
-        <is>
-          <t>54742</t>
-        </is>
-      </c>
-      <c r="M10" s="2" t="inlineStr">
-        <is>
-          <t>73284</t>
-        </is>
-      </c>
-      <c r="N10" s="2" t="inlineStr">
-        <is>
-          <t>49,2%</t>
-        </is>
-      </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>41,85%</t>
+          <t>31,52%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>56,03%</t>
+          <t>47,1%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -3092,12 +3092,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>100957</t>
+          <t>99803</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>125271</t>
+          <t>125316</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -3107,12 +3107,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>39,92%</t>
+          <t>39,47%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>49,54%</t>
+          <t>49,56%</t>
         </is>
       </c>
     </row>
@@ -3125,72 +3125,72 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
+          <t>95</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>66442</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>56838</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>75426</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>50,8%</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>43,45%</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>57,67%</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
           <t>104</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
+      <c r="K11" s="2" t="inlineStr">
         <is>
           <t>73856</t>
         </is>
       </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>64603</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>82474</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
+      <c r="L11" s="2" t="inlineStr">
+        <is>
+          <t>64583</t>
+        </is>
+      </c>
+      <c r="M11" s="2" t="inlineStr">
+        <is>
+          <t>83593</t>
+        </is>
+      </c>
+      <c r="N11" s="2" t="inlineStr">
         <is>
           <t>60,5%</t>
         </is>
       </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>52,92%</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>67,56%</t>
-        </is>
-      </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>95</t>
-        </is>
-      </c>
-      <c r="K11" s="2" t="inlineStr">
-        <is>
-          <t>66442</t>
-        </is>
-      </c>
-      <c r="L11" s="2" t="inlineStr">
-        <is>
-          <t>57515</t>
-        </is>
-      </c>
-      <c r="M11" s="2" t="inlineStr">
-        <is>
-          <t>76057</t>
-        </is>
-      </c>
-      <c r="N11" s="2" t="inlineStr">
-        <is>
-          <t>50,8%</t>
-        </is>
-      </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>43,97%</t>
+          <t>52,9%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>58,15%</t>
+          <t>68,48%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -3205,12 +3205,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>127604</t>
+          <t>127559</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>151918</t>
+          <t>153072</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -3220,12 +3220,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>50,46%</t>
+          <t>50,44%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>60,08%</t>
+          <t>60,53%</t>
         </is>
       </c>
     </row>
@@ -3238,57 +3238,57 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>186</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>130799</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>130799</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>130799</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
           <t>172</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
+      <c r="K12" s="2" t="inlineStr">
         <is>
           <t>122076</t>
         </is>
       </c>
-      <c r="E12" s="2" t="inlineStr">
+      <c r="L12" s="2" t="inlineStr">
         <is>
           <t>122076</t>
         </is>
       </c>
-      <c r="F12" s="2" t="inlineStr">
+      <c r="M12" s="2" t="inlineStr">
         <is>
           <t>122076</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J12" s="2" t="inlineStr">
-        <is>
-          <t>186</t>
-        </is>
-      </c>
-      <c r="K12" s="2" t="inlineStr">
-        <is>
-          <t>130799</t>
-        </is>
-      </c>
-      <c r="L12" s="2" t="inlineStr">
-        <is>
-          <t>130799</t>
-        </is>
-      </c>
-      <c r="M12" s="2" t="inlineStr">
-        <is>
-          <t>130799</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -3355,72 +3355,72 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
+          <t>404</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>280991</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>262542</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>301350</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>50,54%</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>47,22%</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>54,2%</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
           <t>317</t>
         </is>
       </c>
-      <c r="D13" s="2" t="inlineStr">
+      <c r="K13" s="2" t="inlineStr">
         <is>
           <t>222166</t>
         </is>
       </c>
-      <c r="E13" s="2" t="inlineStr">
-        <is>
-          <t>204318</t>
-        </is>
-      </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>242337</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
+      <c r="L13" s="2" t="inlineStr">
+        <is>
+          <t>205399</t>
+        </is>
+      </c>
+      <c r="M13" s="2" t="inlineStr">
+        <is>
+          <t>240883</t>
+        </is>
+      </c>
+      <c r="N13" s="2" t="inlineStr">
         <is>
           <t>42,15%</t>
         </is>
       </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>38,77%</t>
-        </is>
-      </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>45,98%</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>404</t>
-        </is>
-      </c>
-      <c r="K13" s="2" t="inlineStr">
-        <is>
-          <t>280991</t>
-        </is>
-      </c>
-      <c r="L13" s="2" t="inlineStr">
-        <is>
-          <t>260692</t>
-        </is>
-      </c>
-      <c r="M13" s="2" t="inlineStr">
-        <is>
-          <t>300656</t>
-        </is>
-      </c>
-      <c r="N13" s="2" t="inlineStr">
-        <is>
-          <t>50,54%</t>
-        </is>
-      </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>46,89%</t>
+          <t>38,97%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>54,08%</t>
+          <t>45,71%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -3435,12 +3435,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>476298</t>
+          <t>479824</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>532717</t>
+          <t>532637</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -3450,12 +3450,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>43,98%</t>
+          <t>44,31%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>49,19%</t>
+          <t>49,18%</t>
         </is>
       </c>
     </row>
@@ -3468,72 +3468,72 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>394</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>274979</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>254620</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>293428</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>49,46%</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>45,8%</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>52,78%</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
           <t>440</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="K14" s="2" t="inlineStr">
         <is>
           <t>304864</t>
         </is>
       </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>284693</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>322712</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
+      <c r="L14" s="2" t="inlineStr">
+        <is>
+          <t>286147</t>
+        </is>
+      </c>
+      <c r="M14" s="2" t="inlineStr">
+        <is>
+          <t>321631</t>
+        </is>
+      </c>
+      <c r="N14" s="2" t="inlineStr">
         <is>
           <t>57,85%</t>
         </is>
       </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>54,02%</t>
-        </is>
-      </c>
-      <c r="I14" s="2" t="inlineStr">
-        <is>
-          <t>61,23%</t>
-        </is>
-      </c>
-      <c r="J14" s="2" t="inlineStr">
-        <is>
-          <t>394</t>
-        </is>
-      </c>
-      <c r="K14" s="2" t="inlineStr">
-        <is>
-          <t>274979</t>
-        </is>
-      </c>
-      <c r="L14" s="2" t="inlineStr">
-        <is>
-          <t>255314</t>
-        </is>
-      </c>
-      <c r="M14" s="2" t="inlineStr">
-        <is>
-          <t>295278</t>
-        </is>
-      </c>
-      <c r="N14" s="2" t="inlineStr">
-        <is>
-          <t>49,46%</t>
-        </is>
-      </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>45,92%</t>
+          <t>54,29%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>53,11%</t>
+          <t>61,03%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -3548,12 +3548,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>550283</t>
+          <t>550363</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>606702</t>
+          <t>603176</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -3563,12 +3563,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>50,81%</t>
+          <t>50,82%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>56,02%</t>
+          <t>55,69%</t>
         </is>
       </c>
     </row>
@@ -3581,57 +3581,57 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
+          <t>798</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>555970</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>555970</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>555970</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
           <t>757</t>
         </is>
       </c>
-      <c r="D15" s="2" t="inlineStr">
+      <c r="K15" s="2" t="inlineStr">
         <is>
           <t>527030</t>
         </is>
       </c>
-      <c r="E15" s="2" t="inlineStr">
+      <c r="L15" s="2" t="inlineStr">
         <is>
           <t>527030</t>
         </is>
       </c>
-      <c r="F15" s="2" t="inlineStr">
+      <c r="M15" s="2" t="inlineStr">
         <is>
           <t>527030</t>
-        </is>
-      </c>
-      <c r="G15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J15" s="2" t="inlineStr">
-        <is>
-          <t>798</t>
-        </is>
-      </c>
-      <c r="K15" s="2" t="inlineStr">
-        <is>
-          <t>555970</t>
-        </is>
-      </c>
-      <c r="L15" s="2" t="inlineStr">
-        <is>
-          <t>555970</t>
-        </is>
-      </c>
-      <c r="M15" s="2" t="inlineStr">
-        <is>
-          <t>555970</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -3750,7 +3750,7 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -3761,7 +3761,7 @@
       <c r="I1" s="3" t="n"/>
       <c r="J1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="K1" s="3" t="n"/>
@@ -3929,72 +3929,72 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>39</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>28322</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>22419</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>34274</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>52,48%</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>41,54%</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>63,51%</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
           <t>41</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="K4" s="2" t="inlineStr">
         <is>
           <t>27327</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>22090</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>32619</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
+      <c r="L4" s="2" t="inlineStr">
+        <is>
+          <t>21679</t>
+        </is>
+      </c>
+      <c r="M4" s="2" t="inlineStr">
+        <is>
+          <t>32190</t>
+        </is>
+      </c>
+      <c r="N4" s="2" t="inlineStr">
         <is>
           <t>58,25%</t>
         </is>
       </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>47,08%</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>69,53%</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>39</t>
-        </is>
-      </c>
-      <c r="K4" s="2" t="inlineStr">
-        <is>
-          <t>28322</t>
-        </is>
-      </c>
-      <c r="L4" s="2" t="inlineStr">
-        <is>
-          <t>22761</t>
-        </is>
-      </c>
-      <c r="M4" s="2" t="inlineStr">
-        <is>
-          <t>35040</t>
-        </is>
-      </c>
-      <c r="N4" s="2" t="inlineStr">
-        <is>
-          <t>52,48%</t>
-        </is>
-      </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>42,17%</t>
+          <t>46,21%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>64,93%</t>
+          <t>68,61%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -4009,12 +4009,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>47727</t>
+          <t>47590</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>64117</t>
+          <t>63847</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -4024,12 +4024,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>47,31%</t>
+          <t>47,17%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>63,55%</t>
+          <t>63,29%</t>
         </is>
       </c>
     </row>
@@ -4042,72 +4042,72 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
+          <t>38</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>25647</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>19695</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>31550</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>47,52%</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>36,49%</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>58,46%</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
           <t>29</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
+      <c r="K5" s="2" t="inlineStr">
         <is>
           <t>19589</t>
         </is>
       </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>14297</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>24826</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
+      <c r="L5" s="2" t="inlineStr">
+        <is>
+          <t>14726</t>
+        </is>
+      </c>
+      <c r="M5" s="2" t="inlineStr">
+        <is>
+          <t>25237</t>
+        </is>
+      </c>
+      <c r="N5" s="2" t="inlineStr">
         <is>
           <t>41,75%</t>
         </is>
       </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>30,47%</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>52,92%</t>
-        </is>
-      </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>38</t>
-        </is>
-      </c>
-      <c r="K5" s="2" t="inlineStr">
-        <is>
-          <t>25647</t>
-        </is>
-      </c>
-      <c r="L5" s="2" t="inlineStr">
-        <is>
-          <t>18929</t>
-        </is>
-      </c>
-      <c r="M5" s="2" t="inlineStr">
-        <is>
-          <t>31208</t>
-        </is>
-      </c>
-      <c r="N5" s="2" t="inlineStr">
-        <is>
-          <t>47,52%</t>
-        </is>
-      </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>35,07%</t>
+          <t>31,39%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>57,83%</t>
+          <t>53,79%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -4122,12 +4122,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>36768</t>
+          <t>37038</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>53158</t>
+          <t>53295</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -4137,12 +4137,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>36,45%</t>
+          <t>36,71%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>52,69%</t>
+          <t>52,83%</t>
         </is>
       </c>
     </row>
@@ -4155,57 +4155,57 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>77</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>53969</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>53969</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>53969</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
           <t>70</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="K6" s="2" t="inlineStr">
         <is>
           <t>46916</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
+      <c r="L6" s="2" t="inlineStr">
         <is>
           <t>46916</t>
         </is>
       </c>
-      <c r="F6" s="2" t="inlineStr">
+      <c r="M6" s="2" t="inlineStr">
         <is>
           <t>46916</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>77</t>
-        </is>
-      </c>
-      <c r="K6" s="2" t="inlineStr">
-        <is>
-          <t>53969</t>
-        </is>
-      </c>
-      <c r="L6" s="2" t="inlineStr">
-        <is>
-          <t>53969</t>
-        </is>
-      </c>
-      <c r="M6" s="2" t="inlineStr">
-        <is>
-          <t>53969</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -4272,72 +4272,72 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
+          <t>246</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>173046</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>154659</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>188707</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>43,92%</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>39,25%</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>47,89%</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
           <t>189</t>
         </is>
       </c>
-      <c r="D7" s="2" t="inlineStr">
+      <c r="K7" s="2" t="inlineStr">
         <is>
           <t>126505</t>
         </is>
       </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>112405</t>
-        </is>
-      </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>142085</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
+      <c r="L7" s="2" t="inlineStr">
+        <is>
+          <t>112271</t>
+        </is>
+      </c>
+      <c r="M7" s="2" t="inlineStr">
+        <is>
+          <t>142278</t>
+        </is>
+      </c>
+      <c r="N7" s="2" t="inlineStr">
         <is>
           <t>34,11%</t>
         </is>
       </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>30,31%</t>
-        </is>
-      </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>38,31%</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>246</t>
-        </is>
-      </c>
-      <c r="K7" s="2" t="inlineStr">
-        <is>
-          <t>173046</t>
-        </is>
-      </c>
-      <c r="L7" s="2" t="inlineStr">
-        <is>
-          <t>157143</t>
-        </is>
-      </c>
-      <c r="M7" s="2" t="inlineStr">
-        <is>
-          <t>189664</t>
-        </is>
-      </c>
-      <c r="N7" s="2" t="inlineStr">
-        <is>
-          <t>43,92%</t>
-        </is>
-      </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>39,88%</t>
+          <t>30,27%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>48,14%</t>
+          <t>38,36%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -4352,12 +4352,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>279021</t>
+          <t>278038</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>321491</t>
+          <t>321409</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -4367,12 +4367,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>36,48%</t>
+          <t>36,35%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>42,03%</t>
+          <t>42,02%</t>
         </is>
       </c>
     </row>
@@ -4385,72 +4385,72 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>312</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>220976</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>205315</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>239363</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>56,08%</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>52,11%</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>60,75%</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
           <t>365</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="K8" s="2" t="inlineStr">
         <is>
           <t>244362</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>228782</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>258462</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
+      <c r="L8" s="2" t="inlineStr">
+        <is>
+          <t>228589</t>
+        </is>
+      </c>
+      <c r="M8" s="2" t="inlineStr">
+        <is>
+          <t>258596</t>
+        </is>
+      </c>
+      <c r="N8" s="2" t="inlineStr">
         <is>
           <t>65,89%</t>
         </is>
       </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>61,69%</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>69,69%</t>
-        </is>
-      </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>312</t>
-        </is>
-      </c>
-      <c r="K8" s="2" t="inlineStr">
-        <is>
-          <t>220976</t>
-        </is>
-      </c>
-      <c r="L8" s="2" t="inlineStr">
-        <is>
-          <t>204358</t>
-        </is>
-      </c>
-      <c r="M8" s="2" t="inlineStr">
-        <is>
-          <t>236879</t>
-        </is>
-      </c>
-      <c r="N8" s="2" t="inlineStr">
-        <is>
-          <t>56,08%</t>
-        </is>
-      </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>51,86%</t>
+          <t>61,64%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>60,12%</t>
+          <t>69,73%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -4465,12 +4465,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>443398</t>
+          <t>443480</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>485868</t>
+          <t>486851</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -4480,12 +4480,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>57,97%</t>
+          <t>57,98%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>63,52%</t>
+          <t>63,65%</t>
         </is>
       </c>
     </row>
@@ -4498,57 +4498,57 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
+          <t>558</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>394022</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>394022</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>394022</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
           <t>554</t>
         </is>
       </c>
-      <c r="D9" s="2" t="inlineStr">
+      <c r="K9" s="2" t="inlineStr">
         <is>
           <t>370867</t>
         </is>
       </c>
-      <c r="E9" s="2" t="inlineStr">
+      <c r="L9" s="2" t="inlineStr">
         <is>
           <t>370867</t>
         </is>
       </c>
-      <c r="F9" s="2" t="inlineStr">
+      <c r="M9" s="2" t="inlineStr">
         <is>
           <t>370867</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>558</t>
-        </is>
-      </c>
-      <c r="K9" s="2" t="inlineStr">
-        <is>
-          <t>394022</t>
-        </is>
-      </c>
-      <c r="L9" s="2" t="inlineStr">
-        <is>
-          <t>394022</t>
-        </is>
-      </c>
-      <c r="M9" s="2" t="inlineStr">
-        <is>
-          <t>394022</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -4615,72 +4615,72 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>87</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>59805</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>50143</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>69943</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>43,99%</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>36,89%</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>51,45%</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
           <t>53</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="K10" s="2" t="inlineStr">
         <is>
           <t>36034</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>28837</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>45615</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
+      <c r="L10" s="2" t="inlineStr">
+        <is>
+          <t>28356</t>
+        </is>
+      </c>
+      <c r="M10" s="2" t="inlineStr">
+        <is>
+          <t>44930</t>
+        </is>
+      </c>
+      <c r="N10" s="2" t="inlineStr">
         <is>
           <t>28,46%</t>
         </is>
       </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>22,77%</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>36,03%</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>87</t>
-        </is>
-      </c>
-      <c r="K10" s="2" t="inlineStr">
-        <is>
-          <t>59805</t>
-        </is>
-      </c>
-      <c r="L10" s="2" t="inlineStr">
-        <is>
-          <t>49861</t>
-        </is>
-      </c>
-      <c r="M10" s="2" t="inlineStr">
-        <is>
-          <t>69557</t>
-        </is>
-      </c>
-      <c r="N10" s="2" t="inlineStr">
-        <is>
-          <t>43,99%</t>
-        </is>
-      </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>36,68%</t>
+          <t>22,39%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>51,17%</t>
+          <t>35,48%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -4695,12 +4695,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>84065</t>
+          <t>82862</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>109123</t>
+          <t>108073</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -4710,12 +4710,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>32,02%</t>
+          <t>31,56%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>41,56%</t>
+          <t>41,16%</t>
         </is>
       </c>
     </row>
@@ -4728,72 +4728,72 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
+          <t>109</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>76137</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>65999</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>85799</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>56,01%</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>48,55%</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>63,11%</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
           <t>134</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
+      <c r="K11" s="2" t="inlineStr">
         <is>
           <t>90585</t>
         </is>
       </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>81004</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>97782</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
+      <c r="L11" s="2" t="inlineStr">
+        <is>
+          <t>81689</t>
+        </is>
+      </c>
+      <c r="M11" s="2" t="inlineStr">
+        <is>
+          <t>98263</t>
+        </is>
+      </c>
+      <c r="N11" s="2" t="inlineStr">
         <is>
           <t>71,54%</t>
         </is>
       </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>63,97%</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>77,23%</t>
-        </is>
-      </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>109</t>
-        </is>
-      </c>
-      <c r="K11" s="2" t="inlineStr">
-        <is>
-          <t>76137</t>
-        </is>
-      </c>
-      <c r="L11" s="2" t="inlineStr">
-        <is>
-          <t>66385</t>
-        </is>
-      </c>
-      <c r="M11" s="2" t="inlineStr">
-        <is>
-          <t>86081</t>
-        </is>
-      </c>
-      <c r="N11" s="2" t="inlineStr">
-        <is>
-          <t>56,01%</t>
-        </is>
-      </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>48,83%</t>
+          <t>64,52%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>63,32%</t>
+          <t>77,61%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -4808,12 +4808,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>153438</t>
+          <t>154488</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>178496</t>
+          <t>179699</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -4823,12 +4823,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>58,44%</t>
+          <t>58,84%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>67,98%</t>
+          <t>68,44%</t>
         </is>
       </c>
     </row>
@@ -4841,57 +4841,57 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>196</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>135942</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>135942</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>135942</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
           <t>187</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
+      <c r="K12" s="2" t="inlineStr">
         <is>
           <t>126619</t>
         </is>
       </c>
-      <c r="E12" s="2" t="inlineStr">
+      <c r="L12" s="2" t="inlineStr">
         <is>
           <t>126619</t>
         </is>
       </c>
-      <c r="F12" s="2" t="inlineStr">
+      <c r="M12" s="2" t="inlineStr">
         <is>
           <t>126619</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J12" s="2" t="inlineStr">
-        <is>
-          <t>196</t>
-        </is>
-      </c>
-      <c r="K12" s="2" t="inlineStr">
-        <is>
-          <t>135942</t>
-        </is>
-      </c>
-      <c r="L12" s="2" t="inlineStr">
-        <is>
-          <t>135942</t>
-        </is>
-      </c>
-      <c r="M12" s="2" t="inlineStr">
-        <is>
-          <t>135942</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -4958,72 +4958,72 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
+          <t>372</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>261173</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>240456</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>281764</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>44,73%</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>41,18%</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>48,25%</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
           <t>283</t>
         </is>
       </c>
-      <c r="D13" s="2" t="inlineStr">
+      <c r="K13" s="2" t="inlineStr">
         <is>
           <t>189866</t>
         </is>
       </c>
-      <c r="E13" s="2" t="inlineStr">
-        <is>
-          <t>170586</t>
-        </is>
-      </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>208083</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
+      <c r="L13" s="2" t="inlineStr">
+        <is>
+          <t>172831</t>
+        </is>
+      </c>
+      <c r="M13" s="2" t="inlineStr">
+        <is>
+          <t>207961</t>
+        </is>
+      </c>
+      <c r="N13" s="2" t="inlineStr">
         <is>
           <t>34,88%</t>
         </is>
       </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>31,33%</t>
-        </is>
-      </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>38,22%</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>372</t>
-        </is>
-      </c>
-      <c r="K13" s="2" t="inlineStr">
-        <is>
-          <t>261173</t>
-        </is>
-      </c>
-      <c r="L13" s="2" t="inlineStr">
-        <is>
-          <t>241538</t>
-        </is>
-      </c>
-      <c r="M13" s="2" t="inlineStr">
-        <is>
-          <t>281183</t>
-        </is>
-      </c>
-      <c r="N13" s="2" t="inlineStr">
-        <is>
-          <t>44,73%</t>
-        </is>
-      </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>41,36%</t>
+          <t>31,75%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>48,15%</t>
+          <t>38,2%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -5038,12 +5038,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>422726</t>
+          <t>423582</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>477154</t>
+          <t>476396</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -5053,12 +5053,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>37,46%</t>
+          <t>37,54%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>42,29%</t>
+          <t>42,22%</t>
         </is>
       </c>
     </row>
@@ -5071,72 +5071,72 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>459</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>322761</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>302170</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>343478</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>55,27%</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>51,75%</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>58,82%</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
           <t>528</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="K14" s="2" t="inlineStr">
         <is>
           <t>354536</t>
         </is>
       </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>336319</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>373816</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
+      <c r="L14" s="2" t="inlineStr">
+        <is>
+          <t>336441</t>
+        </is>
+      </c>
+      <c r="M14" s="2" t="inlineStr">
+        <is>
+          <t>371571</t>
+        </is>
+      </c>
+      <c r="N14" s="2" t="inlineStr">
         <is>
           <t>65,12%</t>
         </is>
       </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>61,78%</t>
-        </is>
-      </c>
-      <c r="I14" s="2" t="inlineStr">
-        <is>
-          <t>68,67%</t>
-        </is>
-      </c>
-      <c r="J14" s="2" t="inlineStr">
-        <is>
-          <t>459</t>
-        </is>
-      </c>
-      <c r="K14" s="2" t="inlineStr">
-        <is>
-          <t>322761</t>
-        </is>
-      </c>
-      <c r="L14" s="2" t="inlineStr">
-        <is>
-          <t>302751</t>
-        </is>
-      </c>
-      <c r="M14" s="2" t="inlineStr">
-        <is>
-          <t>342396</t>
-        </is>
-      </c>
-      <c r="N14" s="2" t="inlineStr">
-        <is>
-          <t>55,27%</t>
-        </is>
-      </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>51,85%</t>
+          <t>61,8%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>58,64%</t>
+          <t>68,25%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -5151,12 +5151,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>651182</t>
+          <t>651940</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>705610</t>
+          <t>704754</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -5166,12 +5166,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>57,71%</t>
+          <t>57,78%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>62,54%</t>
+          <t>62,46%</t>
         </is>
       </c>
     </row>
@@ -5184,57 +5184,57 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
+          <t>831</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>583934</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>583934</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>583934</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
           <t>811</t>
         </is>
       </c>
-      <c r="D15" s="2" t="inlineStr">
+      <c r="K15" s="2" t="inlineStr">
         <is>
           <t>544402</t>
         </is>
       </c>
-      <c r="E15" s="2" t="inlineStr">
+      <c r="L15" s="2" t="inlineStr">
         <is>
           <t>544402</t>
         </is>
       </c>
-      <c r="F15" s="2" t="inlineStr">
+      <c r="M15" s="2" t="inlineStr">
         <is>
           <t>544402</t>
-        </is>
-      </c>
-      <c r="G15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J15" s="2" t="inlineStr">
-        <is>
-          <t>831</t>
-        </is>
-      </c>
-      <c r="K15" s="2" t="inlineStr">
-        <is>
-          <t>583934</t>
-        </is>
-      </c>
-      <c r="L15" s="2" t="inlineStr">
-        <is>
-          <t>583934</t>
-        </is>
-      </c>
-      <c r="M15" s="2" t="inlineStr">
-        <is>
-          <t>583934</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -5353,7 +5353,7 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -5364,7 +5364,7 @@
       <c r="I1" s="3" t="n"/>
       <c r="J1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="K1" s="3" t="n"/>
@@ -5532,72 +5532,72 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>17350</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>12050</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>23768</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>35,85%</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>24,9%</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>49,11%</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
           <t>20</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
-        <is>
-          <t>17913</t>
-        </is>
-      </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>10227</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>25799</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>38,01%</t>
-        </is>
-      </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>21,7%</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>54,74%</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>25</t>
-        </is>
-      </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>18036</t>
+          <t>14063</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>12695</t>
+          <t>8750</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>24701</t>
+          <t>19634</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>34,63%</t>
+          <t>35,27%</t>
         </is>
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>24,38%</t>
+          <t>21,95%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>47,43%</t>
+          <t>49,24%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -5607,32 +5607,32 @@
       </c>
       <c r="R4" s="2" t="inlineStr">
         <is>
-          <t>35949</t>
+          <t>31413</t>
         </is>
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>26490</t>
+          <t>24255</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>47615</t>
+          <t>39924</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
         <is>
-          <t>36,24%</t>
+          <t>35,59%</t>
         </is>
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>26,7%</t>
+          <t>27,48%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>48,0%</t>
+          <t>45,23%</t>
         </is>
       </c>
     </row>
@@ -5645,72 +5645,72 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
+          <t>43</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>31048</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>24630</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>36348</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>64,15%</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>50,89%</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>75,1%</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
           <t>37</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
-        <is>
-          <t>29218</t>
-        </is>
-      </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>21332</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>36904</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
-        <is>
-          <t>61,99%</t>
-        </is>
-      </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>45,26%</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>78,3%</t>
-        </is>
-      </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>43</t>
-        </is>
-      </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>34041</t>
+          <t>25809</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>27376</t>
+          <t>20238</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>39382</t>
+          <t>31122</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>65,37%</t>
+          <t>64,73%</t>
         </is>
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>52,57%</t>
+          <t>50,76%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>75,62%</t>
+          <t>78,05%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -5720,32 +5720,32 @@
       </c>
       <c r="R5" s="2" t="inlineStr">
         <is>
-          <t>63259</t>
+          <t>56857</t>
         </is>
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>51593</t>
+          <t>48346</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>72718</t>
+          <t>64015</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
         <is>
-          <t>63,76%</t>
+          <t>64,41%</t>
         </is>
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>52,0%</t>
+          <t>54,77%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>73,3%</t>
+          <t>72,52%</t>
         </is>
       </c>
     </row>
@@ -5758,57 +5758,57 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>68</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>48398</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>48398</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>48398</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
           <t>57</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
-        <is>
-          <t>47131</t>
-        </is>
-      </c>
-      <c r="E6" s="2" t="inlineStr">
-        <is>
-          <t>47131</t>
-        </is>
-      </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>47131</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>68</t>
-        </is>
-      </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>52077</t>
+          <t>39872</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>52077</t>
+          <t>39872</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>52077</t>
+          <t>39872</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -5833,17 +5833,17 @@
       </c>
       <c r="R6" s="2" t="inlineStr">
         <is>
-          <t>99208</t>
+          <t>88270</t>
         </is>
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>99208</t>
+          <t>88270</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>99208</t>
+          <t>88270</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -5875,72 +5875,72 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
+          <t>229</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>178873</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>158257</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>202661</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>42,6%</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>37,69%</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>48,26%</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
           <t>166</t>
         </is>
       </c>
-      <c r="D7" s="2" t="inlineStr">
-        <is>
-          <t>112628</t>
-        </is>
-      </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>87441</t>
-        </is>
-      </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>128619</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
-        <is>
-          <t>28,66%</t>
-        </is>
-      </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>22,25%</t>
-        </is>
-      </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>32,73%</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>229</t>
-        </is>
-      </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>191017</t>
+          <t>110861</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>169339</t>
+          <t>97033</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>215052</t>
+          <t>125999</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>42,23%</t>
+          <t>29,98%</t>
         </is>
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>37,43%</t>
+          <t>26,24%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>47,54%</t>
+          <t>34,07%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -5950,32 +5950,32 @@
       </c>
       <c r="R7" s="2" t="inlineStr">
         <is>
-          <t>303645</t>
+          <t>289734</t>
         </is>
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>264947</t>
+          <t>265367</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>333492</t>
+          <t>317506</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
         <is>
-          <t>35,92%</t>
+          <t>36,69%</t>
         </is>
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>31,34%</t>
+          <t>33,6%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>39,45%</t>
+          <t>40,21%</t>
         </is>
       </c>
     </row>
@@ -5988,72 +5988,72 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>325</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>241053</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>217265</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>261669</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>57,4%</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>51,74%</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>62,31%</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
           <t>374</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
-        <is>
-          <t>280305</t>
-        </is>
-      </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>264314</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>305492</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>71,34%</t>
-        </is>
-      </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>67,27%</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>77,75%</t>
-        </is>
-      </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>325</t>
-        </is>
-      </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>261357</t>
+          <t>258929</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>237322</t>
+          <t>243791</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>283035</t>
+          <t>272757</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>57,77%</t>
+          <t>70,02%</t>
         </is>
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>52,46%</t>
+          <t>65,93%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>62,57%</t>
+          <t>73,76%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -6063,32 +6063,32 @@
       </c>
       <c r="R8" s="2" t="inlineStr">
         <is>
-          <t>541662</t>
+          <t>499982</t>
         </is>
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>511815</t>
+          <t>472210</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>580360</t>
+          <t>524349</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
         <is>
-          <t>64,08%</t>
+          <t>63,31%</t>
         </is>
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>60,55%</t>
+          <t>59,79%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>68,66%</t>
+          <t>66,4%</t>
         </is>
       </c>
     </row>
@@ -6101,57 +6101,57 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
+          <t>554</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>419926</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>419926</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>419926</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
           <t>540</t>
         </is>
       </c>
-      <c r="D9" s="2" t="inlineStr">
-        <is>
-          <t>392933</t>
-        </is>
-      </c>
-      <c r="E9" s="2" t="inlineStr">
-        <is>
-          <t>392933</t>
-        </is>
-      </c>
-      <c r="F9" s="2" t="inlineStr">
-        <is>
-          <t>392933</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>554</t>
-        </is>
-      </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>452374</t>
+          <t>369790</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>452374</t>
+          <t>369790</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>452374</t>
+          <t>369790</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -6176,17 +6176,17 @@
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
-          <t>845307</t>
+          <t>789716</t>
         </is>
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>845307</t>
+          <t>789716</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>845307</t>
+          <t>789716</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -6218,72 +6218,72 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>62</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>42896</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>34536</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>53776</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>30,87%</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>24,85%</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>38,69%</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
           <t>47</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
-        <is>
-          <t>31045</t>
-        </is>
-      </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>23216</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>39252</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>23,19%</t>
-        </is>
-      </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>17,34%</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>29,32%</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>62</t>
-        </is>
-      </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>45547</t>
+          <t>30083</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>36110</t>
+          <t>22341</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>56087</t>
+          <t>39531</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>30,69%</t>
+          <t>22,33%</t>
         </is>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>24,33%</t>
+          <t>16,58%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>37,79%</t>
+          <t>29,34%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -6293,32 +6293,32 @@
       </c>
       <c r="R10" s="2" t="inlineStr">
         <is>
-          <t>76593</t>
+          <t>72979</t>
         </is>
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>65240</t>
+          <t>61134</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>91376</t>
+          <t>86879</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
         <is>
-          <t>27,13%</t>
+          <t>26,66%</t>
         </is>
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>23,11%</t>
+          <t>22,34%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>32,37%</t>
+          <t>31,74%</t>
         </is>
       </c>
     </row>
@@ -6331,72 +6331,72 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
+          <t>132</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>96082</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>85202</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>104442</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>69,13%</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>61,31%</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>75,15%</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
           <t>156</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
-        <is>
-          <t>102844</t>
-        </is>
-      </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>94637</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>110673</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
-        <is>
-          <t>76,81%</t>
-        </is>
-      </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>70,68%</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>82,66%</t>
-        </is>
-      </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>132</t>
-        </is>
-      </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>102853</t>
+          <t>104647</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>92313</t>
+          <t>95199</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>112290</t>
+          <t>112389</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>69,31%</t>
+          <t>77,67%</t>
         </is>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>62,21%</t>
+          <t>70,66%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>75,67%</t>
+          <t>83,42%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -6406,32 +6406,32 @@
       </c>
       <c r="R11" s="2" t="inlineStr">
         <is>
-          <t>205697</t>
+          <t>200729</t>
         </is>
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>190914</t>
+          <t>186829</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>217050</t>
+          <t>212574</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
         <is>
-          <t>72,87%</t>
+          <t>73,34%</t>
         </is>
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>67,63%</t>
+          <t>68,26%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>76,89%</t>
+          <t>77,66%</t>
         </is>
       </c>
     </row>
@@ -6444,57 +6444,57 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>194</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>138978</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>138978</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>138978</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
           <t>203</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
-        <is>
-          <t>133889</t>
-        </is>
-      </c>
-      <c r="E12" s="2" t="inlineStr">
-        <is>
-          <t>133889</t>
-        </is>
-      </c>
-      <c r="F12" s="2" t="inlineStr">
-        <is>
-          <t>133889</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J12" s="2" t="inlineStr">
-        <is>
-          <t>194</t>
-        </is>
-      </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>148400</t>
+          <t>134730</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>148400</t>
+          <t>134730</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>148400</t>
+          <t>134730</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -6519,17 +6519,17 @@
       </c>
       <c r="R12" s="2" t="inlineStr">
         <is>
-          <t>282290</t>
+          <t>273708</t>
         </is>
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>282290</t>
+          <t>273708</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>282290</t>
+          <t>273708</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -6561,72 +6561,72 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
+          <t>316</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>239119</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>214496</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>262239</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>39,37%</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>35,32%</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>43,18%</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
           <t>233</t>
         </is>
       </c>
-      <c r="D13" s="2" t="inlineStr">
-        <is>
-          <t>161585</t>
-        </is>
-      </c>
-      <c r="E13" s="2" t="inlineStr">
-        <is>
-          <t>136551</t>
-        </is>
-      </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>184022</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
-        <is>
-          <t>28,15%</t>
-        </is>
-      </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>23,79%</t>
-        </is>
-      </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>32,06%</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>316</t>
-        </is>
-      </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>254601</t>
+          <t>155007</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>228801</t>
+          <t>137244</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>279715</t>
+          <t>173543</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>39,0%</t>
+          <t>28,47%</t>
         </is>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>35,05%</t>
+          <t>25,21%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>42,85%</t>
+          <t>31,88%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -6636,32 +6636,32 @@
       </c>
       <c r="R13" s="2" t="inlineStr">
         <is>
-          <t>416187</t>
+          <t>394126</t>
         </is>
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>379010</t>
+          <t>367009</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>448946</t>
+          <t>423614</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
         <is>
-          <t>33,92%</t>
+          <t>34,22%</t>
         </is>
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>30,89%</t>
+          <t>31,87%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>36,59%</t>
+          <t>36,78%</t>
         </is>
       </c>
     </row>
@@ -6674,72 +6674,72 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>500</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>368183</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>345063</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>392806</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>60,63%</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>56,82%</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>64,68%</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
           <t>567</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
-        <is>
-          <t>412368</t>
-        </is>
-      </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>389931</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>437402</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
-        <is>
-          <t>71,85%</t>
-        </is>
-      </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>67,94%</t>
-        </is>
-      </c>
-      <c r="I14" s="2" t="inlineStr">
-        <is>
-          <t>76,21%</t>
-        </is>
-      </c>
-      <c r="J14" s="2" t="inlineStr">
-        <is>
-          <t>500</t>
-        </is>
-      </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>398251</t>
+          <t>389384</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>373137</t>
+          <t>370848</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>424051</t>
+          <t>407147</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>61,0%</t>
+          <t>71,53%</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>57,15%</t>
+          <t>68,12%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>64,95%</t>
+          <t>74,79%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -6749,32 +6749,32 @@
       </c>
       <c r="R14" s="2" t="inlineStr">
         <is>
-          <t>810618</t>
+          <t>757567</t>
         </is>
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>777859</t>
+          <t>728079</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>847795</t>
+          <t>784684</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
         <is>
-          <t>66,08%</t>
+          <t>65,78%</t>
         </is>
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>63,41%</t>
+          <t>63,22%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>69,11%</t>
+          <t>68,13%</t>
         </is>
       </c>
     </row>
@@ -6787,57 +6787,57 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
+          <t>816</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>607302</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>607302</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>607302</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
           <t>800</t>
         </is>
       </c>
-      <c r="D15" s="2" t="inlineStr">
-        <is>
-          <t>573953</t>
-        </is>
-      </c>
-      <c r="E15" s="2" t="inlineStr">
-        <is>
-          <t>573953</t>
-        </is>
-      </c>
-      <c r="F15" s="2" t="inlineStr">
-        <is>
-          <t>573953</t>
-        </is>
-      </c>
-      <c r="G15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J15" s="2" t="inlineStr">
-        <is>
-          <t>816</t>
-        </is>
-      </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>652852</t>
+          <t>544391</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>652852</t>
+          <t>544391</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>652852</t>
+          <t>544391</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -6862,17 +6862,17 @@
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t>1226805</t>
+          <t>1151693</t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>1226805</t>
+          <t>1151693</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>1226805</t>
+          <t>1151693</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
